--- a/output/pdf_financials_xlsx/SOU.xlsx
+++ b/output/pdf_financials_xlsx/SOU.xlsx
@@ -7908,16 +7908,16 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.373855</v>
+        <v>-0.364887</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-1.15468</v>
+        <v>0.457236</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>-0.606802</v>
+        <v>0.396346</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-0.689357</v>
+        <v>-0.45193</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>-2.960971</v>
@@ -50538,7 +50538,11 @@
           <t>Exploration and evaluation expenses</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E396" t="inlineStr">
         <is>
           <t>-</t>
@@ -55188,7 +55192,11 @@
           <t>Exploration and evaluation expenses 1,611,916</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -57130,7 +57138,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E458" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SOU.xlsx
+++ b/output/pdf_financials_xlsx/SOU.xlsx
@@ -984,13 +984,13 @@
         <v>2.161996</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>3.303369</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>3.835617</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1.275939</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>2.818</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.813353</v>
+        <v>-3.022264</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.765</v>
+        <v>-0.510939</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-2.16</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>6.096631</v>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>6.096631</v>
@@ -8314,25 +8314,25 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.415</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.299</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.227</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="125">
@@ -8377,25 +8377,25 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.415</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.299</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.227</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.141</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.134</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.095</v>
       </c>
     </row>
     <row r="126">
@@ -30112,7 +30112,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -33258,7 +33258,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -35306,7 +35310,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E252" t="inlineStr">
         <is>
           <t>-</t>
@@ -41328,7 +41336,11 @@
           <t>Finance lease payments</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -43548,7 +43560,11 @@
           <t>Finance lease payments (Note 5)</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -45452,7 +45468,11 @@
           <t>Finance lease payments (Note 6)</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E348" t="inlineStr">
         <is>
           <t>-</t>
@@ -78338,7 +78358,7 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
@@ -79826,7 +79846,7 @@
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
@@ -84764,7 +84784,7 @@
       </c>
       <c r="D721" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E721" t="inlineStr">
@@ -92430,7 +92450,7 @@
       </c>
       <c r="D793" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E793" t="inlineStr">

--- a/output/pdf_financials_xlsx/SOU.xlsx
+++ b/output/pdf_financials_xlsx/SOU.xlsx
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>2.691396</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>-0.00212</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -59704,7 +59704,11 @@
           <t>Issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E482" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SOU.xlsx
+++ b/output/pdf_financials_xlsx/SOU.xlsx
@@ -1380,7 +1380,7 @@
         <v>-2.695</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>-10.873</v>
+        <v>-11.083</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>-7.813</v>
@@ -1421,7 +1421,7 @@
         <v>0.06390899999999999</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.239248</v>
+        <v>-0.557205</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0.511888</v>
@@ -1433,7 +1433,7 @@
         <v>-0</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.16225</v>
+        <v>-0.16225</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1445,7 +1445,7 @@
         <v>-0</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-0</v>
+        <v>0.21</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>-0</v>
@@ -1699,13 +1699,13 @@
         <v>-0.606</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-2.695</v>
+        <v>-2.16</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-10.873</v>
+        <v>-10.896</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-7.813</v>
+        <v>-11.31</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>10.093</v>
@@ -2211,7 +2211,7 @@
         <v>-2.695</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-10.873</v>
+        <v>-11.083</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-7.813</v>
@@ -2339,7 +2339,7 @@
         <v>-2.568</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.132</v>
+        <v>-5.342</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-4.066</v>
@@ -2412,7 +2412,7 @@
         <v>-390.2735562310031</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-33.60838244924689</v>
+        <v>-34.98362802881466</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-48.91134367857573</v>
@@ -2453,7 +2453,7 @@
         <v>25.85378285880725</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-7.770554791394993</v>
+        <v>-18.09750544430569</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-20.57533506546961</v>
@@ -2477,7 +2477,7 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.894793828385816</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>-0</v>
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.004587</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>-0.07965800000000001</v>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.082456</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -32956,7 +32956,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -44624,7 +44628,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E340" t="inlineStr">
         <is>
           <t>-</t>
@@ -45152,7 +45160,11 @@
           <t>Proceeds from share issuances, net (Note 10)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -49290,7 +49302,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -50352,7 +50368,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -53396,7 +53416,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -54892,7 +54916,11 @@
           <t>Deferred income tax expense (recovery) 511,888</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -58012,7 +58040,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -58750,7 +58782,11 @@
           <t>Changes in non-cash operating working capital (note 11)</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
@@ -59380,7 +59416,11 @@
           <t>Proceeds on sale of investments (note 4(b))</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -60350,7 +60390,11 @@
           <t>Future income tax expense 63,909</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -61216,7 +61260,11 @@
           <t>Proceeds on sale of investments (Note 9) 2,082,456</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -73318,7 +73366,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D612" t="inlineStr"/>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E612" t="inlineStr">
         <is>
           <t>-</t>
@@ -74684,7 +74736,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D625" t="inlineStr"/>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E625" t="inlineStr">
         <is>
           <t>-</t>
@@ -74790,7 +74846,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D626" t="inlineStr"/>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E626" t="inlineStr">
         <is>
           <t>-</t>
@@ -81206,7 +81266,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E687" t="inlineStr">
         <is>
           <t>-</t>
@@ -82878,7 +82942,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E703" t="inlineStr">
         <is>
           <t>-</t>
@@ -88516,7 +88584,11 @@
           <t>Deferred income tax recovery 10</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E756" t="inlineStr">
         <is>
           <t>-</t>
